--- a/diseases/d085/2010-2014.xlsx
+++ b/diseases/d085/2010-2014.xlsx
@@ -8715,6 +8715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9571,6 +9576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10899,6 +10909,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11519,6 +11534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19134,6 +19154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19282,6 +19307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19430,6 +19460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19578,6 +19613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27193,6 +27233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27341,6 +27386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27489,6 +27539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27637,6 +27692,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27785,6 +27845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27933,6 +27998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36180,6 +36250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36328,6 +36403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36476,6 +36556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36624,6 +36709,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36772,6 +36862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36920,6 +37015,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37068,6 +37168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37216,6 +37321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37364,6 +37474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37512,6 +37627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46162,6 +46282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46310,6 +46435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46458,6 +46588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46606,6 +46741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46754,6 +46894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46902,6 +47047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47050,6 +47200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47198,6 +47353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47344,6 +47504,11 @@
       <c r="S244" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
